--- a/r4-core-main/all-profiles.xlsx
+++ b/r4-core-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-22T15:25:29+00:00</t>
+    <t>2024-10-26T11:41:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -15638,7 +15638,7 @@
         <v>76</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>23</v>

--- a/r4-core-main/all-profiles.xlsx
+++ b/r4-core-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T11:41:35+00:00</t>
+    <t>2024-10-26T12:52:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/all-profiles.xlsx
+++ b/r4-core-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-26T12:52:52+00:00</t>
+    <t>2024-10-26T13:45:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/all-profiles.xlsx
+++ b/r4-core-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:36:22+00:00</t>
+    <t>2024-11-17T21:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/all-profiles.xlsx
+++ b/r4-core-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T21:23:25+00:00</t>
+    <t>2024-11-27T13:38:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/all-profiles.xlsx
+++ b/r4-core-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-27T13:38:13+00:00</t>
+    <t>2024-12-15T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1468,10 +1468,10 @@
     <t>Organization.identifier:KANR.system</t>
   </si>
   <si>
-    <t>OID for the Austrian Federal Ministry of Health</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.40.0.34.3.1.1</t>
+    <t>OID for the Krankenanstaltennummer (KA-Nr) in Austria</t>
+  </si>
+  <si>
+    <t>urn:oid:1.2.40.0.34.4.10</t>
   </si>
   <si>
     <t>Organization.identifier:KANR.value</t>

--- a/r4-core-main/all-profiles.xlsx
+++ b/r4-core-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-15T13:48:39+00:00</t>
+    <t>2024-12-19T09:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -52068,7 +52068,7 @@
         <v>76</v>
       </c>
       <c r="H429" t="s" s="2">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="I429" t="s" s="2">
         <v>23</v>

--- a/r4-core-main/all-profiles.xlsx
+++ b/r4-core-main/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-08T15:19:00+00:00</t>
+    <t>2025-01-24T15:25:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/all-profiles.xlsx
+++ b/r4-core-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T15:25:06+00:00</t>
+    <t>2025-01-27T07:42:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/all-profiles.xlsx
+++ b/r4-core-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T07:42:42+00:00</t>
+    <t>2025-01-27T10:22:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/all-profiles.xlsx
+++ b/r4-core-main/all-profiles.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T10:22:54+00:00</t>
+    <t>2025-01-27T12:06:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-core-main/all-profiles.xlsx
+++ b/r4-core-main/all-profiles.xlsx
@@ -30,7 +30,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-address</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-address</t>
   </si>
   <si>
     <t>Version</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T10:57:38+00:00</t>
+    <t>2026-08-11T12:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -332,7 +332,7 @@
     <t>municipalityCode</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-address-municipalityCode}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-address-municipalityCode}
 </t>
   </si>
   <si>
@@ -500,7 +500,7 @@
     <t>additionalInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-address-additionalInformation}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-address-additionalInformation}
 </t>
   </si>
   <si>
@@ -626,7 +626,7 @@
     <t>at-core-ext-address-additionalInformation</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-address-additionalInformation</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-address-additionalInformation</t>
   </si>
   <si>
     <t>AddressAdditionalInformation</t>
@@ -647,7 +647,7 @@
     <t>element:Address.line</t>
   </si>
   <si>
-    <t>element:http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-address#Address.line</t>
+    <t>element:https://fhir.hl7.at/core/r4/StructureDefinition/at-core-address#Address.line</t>
   </si>
   <si>
     <t>Extension.id</t>
@@ -684,7 +684,7 @@
     <t>at-core-ext-address-municipalityCode</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-address-municipalityCode</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-address-municipalityCode</t>
   </si>
   <si>
     <t>AddressMunicipalityCode</t>
@@ -693,13 +693,13 @@
     <t>element:Address</t>
   </si>
   <si>
-    <t>element:http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-address#Address</t>
+    <t>element:https://fhir.hl7.at/core/r4/StructureDefinition/at-core-address#Address</t>
   </si>
   <si>
     <t>at-core-ext-gender-administrativeGenderAddition</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-gender-administrativeGenderAddition</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-gender-administrativeGenderAddition</t>
   </si>
   <si>
     <t>AdministrativeGenderAddition</t>
@@ -727,13 +727,13 @@
     <t>element:Person.gender</t>
   </si>
   <si>
-    <t>element:http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient#Patient.gender</t>
-  </si>
-  <si>
-    <t>element:http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient#Patient.contact.gender</t>
-  </si>
-  <si>
-    <t>element:http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner#Practitioner.gender</t>
+    <t>element:https://fhir.hl7.at/core/r4/StructureDefinition/at-core-patient#Patient.gender</t>
+  </si>
+  <si>
+    <t>element:https://fhir.hl7.at/core/r4/StructureDefinition/at-core-patient#Patient.contact.gender</t>
+  </si>
+  <si>
+    <t>element:https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitioner#Practitioner.gender</t>
   </si>
   <si>
     <t xml:space="preserve">Coding
@@ -750,7 +750,7 @@
     <t>at-core-ext-patient-religion</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-patient-religion</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-patient-religion</t>
   </si>
   <si>
     <t>PatientReligion</t>
@@ -769,7 +769,7 @@
     <t>element:Patient</t>
   </si>
   <si>
-    <t>element:http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient#Patient</t>
+    <t>element:https://fhir.hl7.at/core/r4/StructureDefinition/at-core-patient#Patient</t>
   </si>
   <si>
     <t>Extension.extension:code</t>
@@ -843,7 +843,7 @@
     <t>at-core-ext-valueset-systemoid</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-valueset-systemoid</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-valueset-systemoid</t>
   </si>
   <si>
     <t>SystemOID</t>
@@ -862,10 +862,10 @@
     <t>element:ValueSet.expansion.contains</t>
   </si>
   <si>
-    <t>element:http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-valueset#ValueSet.compose.include</t>
-  </si>
-  <si>
-    <t>element:http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-valueset#ValueSet.expansion.contains</t>
+    <t>element:https://fhir.hl7.at/core/r4/StructureDefinition/at-core-valueset#ValueSet.compose.include</t>
+  </si>
+  <si>
+    <t>element:https://fhir.hl7.at/core/r4/StructureDefinition/at-core-valueset#ValueSet.expansion.contains</t>
   </si>
   <si>
     <t xml:space="preserve">oid
@@ -875,7 +875,7 @@
     <t>at-core-location</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-location</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-location</t>
   </si>
   <si>
     <t>HL7ATCoreLocation</t>
@@ -1449,7 +1449,7 @@
     <t>Location.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-address}
+    <t xml:space="preserve">Address {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-address}
 </t>
   </si>
   <si>
@@ -1559,7 +1559,7 @@
     <t>Location.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r4/StructureDefinition/at-core-organization)
 </t>
   </si>
   <si>
@@ -1578,7 +1578,7 @@
     <t>Location.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-location)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r4/StructureDefinition/at-core-location)
 </t>
   </si>
   <si>
@@ -1691,7 +1691,7 @@
     <t>at-core-organization</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-organization</t>
   </si>
   <si>
     <t>HL7ATCoreOrganization</t>
@@ -2251,7 +2251,7 @@
     <t>at-core-patient</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-patient</t>
   </si>
   <si>
     <t>HL7ATCorePatient</t>
@@ -3203,7 +3203,7 @@
     <t>Patient.gender.extension:AdministrativeGenderAddition</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-gender-administrativeGenderAddition}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-gender-administrativeGenderAddition}
 </t>
   </si>
   <si>
@@ -3908,7 +3908,7 @@
     <t>at-core-practitioner</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitioner</t>
   </si>
   <si>
     <t>HL7ATCorePractitioner</t>
@@ -4349,7 +4349,7 @@
     <t>at-core-practitionerRole</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitionerRole</t>
   </si>
   <si>
     <t>HL7ATCorePractitionerRole</t>
@@ -4436,7 +4436,7 @@
     <t>PractitionerRole.practitioner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/core/r4/StructureDefinition/at-core-practitioner)
 </t>
   </si>
   <si>
@@ -4639,7 +4639,7 @@
     <t>at-core-valueset</t>
   </si>
   <si>
-    <t>http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-valueset</t>
+    <t>https://fhir.hl7.at/core/r4/StructureDefinition/at-core-valueset</t>
   </si>
   <si>
     <t>HL7ATCoreValueSet</t>
@@ -5022,7 +5022,7 @@
     <t>systemOID</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-ext-valueset-systemoid}
+    <t xml:space="preserve">Extension {https://fhir.hl7.at/core/r4/StructureDefinition/at-core-ext-valueset-systemoid}
 </t>
   </si>
   <si>

--- a/r4-core-main/all-profiles.xlsx
+++ b/r4-core-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T12:53:53+00:00</t>
+    <t>2026-08-20T09:19:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -40674,7 +40674,7 @@
       </c>
       <c r="F314" s="2"/>
       <c r="G314" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H314" t="s" s="2">
         <v>77</v>
@@ -42564,7 +42564,7 @@
       </c>
       <c r="F332" s="2"/>
       <c r="G332" t="s" s="2">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="H332" t="s" s="2">
         <v>85</v>
